--- a/output/pdf_financials_xlsx/CPKR.xlsx
+++ b/output/pdf_financials_xlsx/CPKR.xlsx
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>24.389</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>24.389</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>194.849</v>
+        <v>170.46</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>225.94</v>
+        <v>171.66</v>
       </c>
     </row>
     <row r="49">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">

--- a/output/pdf_financials_xlsx/CPKR.xlsx
+++ b/output/pdf_financials_xlsx/CPKR.xlsx
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>11.34</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>3.803</v>
       </c>
     </row>
     <row r="41">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>85.56999999999999</v>
+        <v>96.91</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>100.637</v>
+        <v>104.44</v>
       </c>
     </row>
     <row r="42">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>170.46</v>
+        <v>159.12</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>171.66</v>
+        <v>167.857</v>
       </c>
     </row>
     <row r="49">
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>20.844</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>24.409</v>
       </c>
     </row>
     <row r="71">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>20.844</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>24.409</v>
       </c>
     </row>
     <row r="72">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.3489724699495929</v>
+        <v>8.431174873982163</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>1.456023148420495</v>
+        <v>1.54576739808224</v>
       </c>
     </row>
     <row r="81">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-23.381</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>25.042</v>
       </c>
     </row>
     <row r="107">
@@ -3388,7 +3388,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>20.844</v>
       </c>
@@ -4060,7 +4064,11 @@
           <t>Deferred income tax expense 12</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>12.671</v>
       </c>
@@ -4388,7 +4396,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>-23.381</v>
       </c>
